--- a/keywords_output.xlsx
+++ b/keywords_output.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$F$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,11 +432,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="89" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="53" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -478,14 +478,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>595cc开元官网版下载</t>
+          <t>星空入口</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lỗi: Page.goto: Target page, context or browser has been closed
-Call log:
-  - navigat</t>
+          <t>Lỗi: Không thể thực hiện tìm kiếm chi tiết</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -493,19 +491,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>595cc开元官网版下载app2026最新版下载v.{getone name="diy:bben" cacheid="1"/} 安卓版-2265安卓网</t>
+          <t>星空入口-星空入口官方最新版2026V{getone name="diy:bben" cacheid="1"/} 安卓版-2265安卓网</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>星空入口</t>
+          <t>ayx游戏app官方版</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lỗi: Page.goto: Target page, context or browser has been closed</t>
+          <t>Lỗi: Không thể tạo page mới</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -520,12 +518,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kiayun登录入口登录</t>
+          <t>hth网页版在线登录入口</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lỗi: Page.goto: Target page, context or browser has been closed</t>
+          <t>Lỗi: Không thể tạo page mới</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -540,12 +538,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>星空手机网页版</t>
+          <t>星空·体育中国综合</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lỗi: Page.goto: Target page, context or browser has been closed</t>
+          <t>Lỗi: Không thể tạo page mới</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -557,8 +555,53 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>星空官方app下载</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lỗi: Không thể tạo page mới</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>开云足球</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lỗi: Không thể tạo page mới</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>米兰电竞</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lỗi: Không thể tạo page mới</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/keywords_output.xlsx
+++ b/keywords_output.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$F$206</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,11 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FF0000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -59,11 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -432,15 +438,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="53" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="100" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,132 +482,2407 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>星空入口</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1155电子游戏官网入口</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lỗi: Không thể thực hiện tìm kiếm chi tiết</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FFFF0000"/>
+            </rPr>
+            <t>1155电子游戏官网入口</t>
+          </r>
+          <r>
+            <t>手机版-1155电子游戏官网入口官方版下载V</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FFFF0000"/>
+            </rPr>
+            <t>{getone name="diy:banben" cacheid="1"/} 安卓版-2265安卓网</t>
+          </r>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>www.kfm96.com</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>星空入口-星空入口官方最新版2026V{getone name="diy:bben" cacheid="1"/} 安卓版-2265安卓网</t>
-        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ayx游戏app官方版</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Lỗi: Không thể tạo page mới</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
+          <t>17CC一起起草平台登录步骤</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>星空入口-星空入口官方最新版2026V{getone name="diy:bben" cacheid="1"/} 安卓版-2265安卓网</t>
-        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hth网页版在线登录入口</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lỗi: Không thể tạo page mới</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
+          <t>17ccom登录方法2</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>kiayun登录入口登录官方版-kiayun登录入口登录2026最新版 v{getone name="diy:bben" cacheid="1"/} 安卓版-2265安卓网</t>
-        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>星空·体育中国综合</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Lỗi: Không thể tạo page mới</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
+          <t>17c官方网页版进入</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>4</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>星空手机网页版登录入口-星空手机网页版登录入口最新版V{getone name="diy:bben" cacheid="1"/} 安卓版-2265安卓网</t>
-        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>星空官方app下载</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Lỗi: Không thể tạo page mới</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
+          <t>17c网页版最新登录地址在哪</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>开云足球</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Lỗi: Không thể tạo page mới</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
+          <t>19616801登录入口</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>米兰电竞</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Lỗi: Không thể tạo page mới</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
+          <t>1pgbet电子麻将胡了官网入口</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>7</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1pg·bet登录</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1pg电子麻将胡了官网入口</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>28圈pg电子游戏在线玩</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>67381·cmo顶级游戏娱乐平台</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6Y·CL模拟器</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7c娱乐app官网下载</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>7c娱乐最新版下载</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>C7.C7.cpp</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>C7C7CPP</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C7C7app官方下载</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C7app下载安装</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C7在线登录</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C7大舞台下载</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C7大舞台下载链接最新版</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C7娱乐APP怎么下载</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C7娱乐下载官网APP入口</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>C7娱乐官网入口在哪</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>C7娱乐平台app最新版本更新内容</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C7娱乐最新2025下载</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>C7娱乐最新版本下载</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C7娱乐游戏 官网</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>C7官方下载</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>C7官方网站登录入口</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>C7官网版</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C7电子娱乐连接</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C7网页版链接</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Hg模拟器</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>JDB爆分大奖视频</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>第一彩民知道!JDB 爆分大奖视频 - 哔哩哔哩</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>www.bilibili.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>近期发布</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LG电子游戏</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MG冰球突破大奖视频</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026第一科普:mg冰球突破大奖视频_暗黑破坏神 | 大神</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>m.ds.163.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>近期发布</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MG爆大奖视频</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Mg大奖视频</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PC娱乐场官网下载</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PC模拟器手机版下载</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PC模拟器游戏资源</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>pc模拟器游戏资源分享的个人空间-pc模拟器游戏资源分享个人主页...</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>m.bilibili.com</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PG397官方正版下载入口</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PG99模拟器</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PGsfot</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PG·澳威尼斯游戏</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PG亡灵大盗爆分时间</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PG加拿大2.8模拟器</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PG哪个三个夺宝爆率高</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PG在线玩模拟版</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>PG天天输是人为控制吗</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FFFF0000"/>
+            </rPr>
+            <t>PG天天输是人为控制吗</t>
+          </r>
+          <r>
+            <t>|?老玩家亲测揭秘:背后真相竟和...</t>
+          </r>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>gd.huatu.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>近期发布</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>PG夺宝赏金女王</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FFFF0000"/>
+            </rPr>
+            <t>PG夺宝赏金女王</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> - 图片</t>
+          </r>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PG娱乐场</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PG娱乐官网下载</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PG官网网站</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PG新人注册28元礼金在哪找</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PG新游</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PG模拟器(无限金币)</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PG模拟器免费</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PG模拟器入口无需下载</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PG模拟器在线玩的网站</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PG模拟器安卓APK</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PG模拟器安卓版</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PG游戏充虎牙币</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PG游戏官网入口</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026第一盘点:电子pg游戏官网入口</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>www.zhihu.com</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PG游戏无限金币</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PG澳门电子</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PG澳门电子游戏</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PG电子·麻将胡了2下载</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PG电子·麻将胡了下载</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PG电子壹号</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PG电子娱乐平台游戏</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PG电子娱乐游戏</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PG电子娱乐游戏平台</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PG电子娱乐澳门网址</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PG电子是怎么控制输赢的</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PG电子最新游戏</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PG电子模拟器试玩版</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PG电子游戏APP</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PG电子游戏APP入口</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PG电子游戏平台</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PG电子游戏是干嘛的</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PG电子绝地大逃杀小游戏</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PG电子要开加速吗</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PG电子要开加速模式吗</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PG电子要开加速模式好不好</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PG电子要开加速的利与弊</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>PG电子财神到</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FFFF0000"/>
+            </rPr>
+            <t>PG电子财神到</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> - 图片</t>
+          </r>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PG电子赏金国际APP下载入口</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>PG电子高爆平</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026第一了解!PG电子高爆平台_暗黑破坏神 | 大神</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ds.163.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>近期发布</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PG电游网</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>pg电游网,一款汇聚潮流与创新的应用,带你领略科技与...</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>www.jyb.cn</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PG的游戏可以获得免费旋转</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PG的游戏哪个爆率高</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>PG的游戏玩法和规则</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>PG赌博官网app下载</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>PG赏金女王官方下载</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>PG赢钱技巧十句口诀</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FFFF0000"/>
+            </rPr>
+            <t>PG赢钱技巧十句口诀</t>
+          </r>
+          <r>
+            <t>——内行人私藏的实战干货,句句实用,新手轻松...</t>
+          </r>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>gd.huatu.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>近期发布</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>PG输了罚多少</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FFFF0000"/>
+            </rPr>
+            <t>PG输了罚多少</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> - 百度问一问</t>
+          </r>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>PG问鼎国际(PG)</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>PG麻将胡了2(官方版)</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>PG麻将胡了无限金币网站</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>PG麻将胡了试玩版</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Pg游戏平台有哪些</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Pg游戏怎么藏分</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>3分钟了解:pg游戏怎么藏分 | VK</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>vk.com</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Pg游戏攻略</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>p g 游 戏 攻 略 大 全</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>weibo.com</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Pg游戏是什么意思</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Pg游戏是什么游戏</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Pg电子招财猫</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>【第一彩民教程】PG 电子招财猫视频 - 哔哩哔哩</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>www.bilibili.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>近期发布</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Pg电子模拟器网站入口</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Pg电子游戏模拟器怎么安装</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FFFF0000"/>
+            </rPr>
+            <t>Pg电子游戏模拟器怎么安装</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> - 图片</t>
+          </r>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Pg麻将胡了免费入口</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>TG模拟器</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>apple ii模拟器</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>app下载苹果版</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>aps3e模拟器官网入口</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>c 7电子娱乐</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>c7.cnm娱乐游戏网页</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>c7app下载安装最新版</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>c7c7..ccm.</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>c7c7.apo.ccm.浏览器打开方式</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>c7c7.apo.ccmc7c7.apo.ccm.</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>c7c7.aqq.ccm/登录入口</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>c7c7vip21.ccm.</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>c7com登录入口</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>c7体育官网入口地址</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>c7南宫娱乐官网</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>c7国际下载</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>c7大舞台官方连接</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>c7大舞台注册</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>c7娱乐国际</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>c7娱乐在线游戏</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>c7娱乐游戏登录入口</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>c7娱乐电子游戏入口</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>c7客服如何联系</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>c7平台的登录入口在哪里</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>c7是什么意思</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>龋齿c7是什么意思-口腔科-博禾医生</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>m.bohe.cn</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>近期发布</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>c7注册入口安装</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>c7注册入口官网地址</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>c7注册入口官网注册官方版</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>c7游戏链接</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>限量版收藏!C7游戏链接迷你冰箱模型DIY过程</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>c7电子游戏入口</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>c7登录网页入口</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>c7线上链接</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>c7网页登录入口地址游戏</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>gg模拟器</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>k7网页登录入口地址是什么</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>mg免费游戏试玩</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FFFF0000"/>
+            </rPr>
+            <t>mg免费游戏试玩</t>
+          </r>
+          <r>
+            <t>平台2026最新版下载v</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FFFF0000"/>
+            </rPr>
+            <t>{getone name="diy:banben" cacheid="1"/} 安卓版-2265安卓网</t>
+          </r>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>www.yuanyang.gov.cn</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>近期发布</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>mg大爆分视频</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>mg豪华大奖视频</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>oppo手机怎么取消安全模式</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>pG模拟器在线玩</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>pG模拟器无限金币</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>pG模拟器试玩入口免费</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>pG电子模拟器网站</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>pG电子游戏入口</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>科普第一!PG电子游戏入口在哪里 - 哔哩哔哩</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>www.bilibili.com</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>pG电子游戏软件平台</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>pG试玩版无限金币</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>pG麻将胡了视频</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>pc免费送2000试玩金</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>pc模拟器下载</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FFFF0000"/>
+            </rPr>
+            <t>pc模拟器下载</t>
+          </r>
+          <r>
+            <t>-征途官方网站-腾讯游戏</t>
+          </r>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>zt.qq.com</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>pc模拟器免费版</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>pc模拟器手机版下载</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>pc模拟器手机版下载安装</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>pc游戏免费网站</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>pg soft下载</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>pg soft游戏</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>pg.168模拟器官网</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>pg168.pot电子模拟器</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Windows的各种扩展名详解_pg168.pot电子模拟器-CSDN博客</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>blog.csdn.net</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>pg28娱乐游戏官网</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>pg360转体扣篮</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>pgc7模拟器试玩入口</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>pgc电子模拟器试玩</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>pgm模拟器下载</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>pgm模拟器在线玩</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>pgm游戏模拟器安卓版</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>pgsoft官方下载入口</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>pg什么游戏好玩</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>pg免费体验版模拟器</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>pg免费游戏试玩平台</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>pg免费游戏试玩版网站app</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>pg免费游戏试玩网页版</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>pg免费送2000试玩金</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>pg免费送2000试玩金游戏特色</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>pg冰雪大闯关电子游戏</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026课堂/第一:pg冰雪大闯关电子游戏大奖爆分 - 哔哩哔哩</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>www.bilibili.com</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>近期发布</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>pg几点最容易爆奖啊</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>pg包赢教程</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>pg单机版游戏</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>pg哪个台子可以用顺意卡</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>pg哪个游戏容易爆分</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>pg哪个游戏爆率高</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>pg大赢家麻将胡了免费下载</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>pg夺宝女王安卓版下载</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>pg夺宝赏金女王官方下载</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>pg夺宝赏金女王官方下载网址</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>pg夺宝赏金女王官方网站</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>pg夺宝赏金女王官方网站入口</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>pg女王夺宝模拟器</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>pg女王夺宝模拟器入口</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>pg女王夺宝模拟器链接</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>pg女王怎么拉爆率高</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>pg女王模拟器免费版</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>pg女王模拟器试玩入口官网</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>pg娱乐游戏平台游戏</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>pg娱乐电子游戏app麻将胡了</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>pg娱乐诚游戏</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Lỗi: Bị captcha Baidu</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="n">
+        <v>205</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F206"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>